--- a/Result/04-07-25/NASDAQstock_04-07-25period252RS90.xlsx
+++ b/Result/04-07-25/NASDAQstock_04-07-25period252RS90.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/04-07-25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2067471-BE11-4741-ADAB-B1521108346F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06927B88-C3B5-F040-98FC-24AF7FBE3076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -962,7 +962,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -985,6 +985,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1024,7 +1030,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1035,6 +1041,8 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1469,7 +1477,7 @@
       </c>
     </row>
     <row r="2" spans="1:42">
-      <c r="A2" t="s">
+      <c r="A2" s="8" t="s">
         <v>42</v>
       </c>
       <c r="B2">
@@ -1594,7 +1602,7 @@
       </c>
     </row>
     <row r="3" spans="1:42">
-      <c r="A3" t="s">
+      <c r="A3" s="8" t="s">
         <v>47</v>
       </c>
       <c r="B3">
@@ -1719,7 +1727,7 @@
       </c>
     </row>
     <row r="4" spans="1:42">
-      <c r="A4" t="s">
+      <c r="A4" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B4">
@@ -1844,7 +1852,7 @@
       </c>
     </row>
     <row r="5" spans="1:42">
-      <c r="A5" t="s">
+      <c r="A5" s="8" t="s">
         <v>54</v>
       </c>
       <c r="B5">
@@ -2094,7 +2102,7 @@
       </c>
     </row>
     <row r="7" spans="1:42">
-      <c r="A7" t="s">
+      <c r="A7" s="8" t="s">
         <v>62</v>
       </c>
       <c r="B7">
@@ -2222,7 +2230,7 @@
       </c>
     </row>
     <row r="8" spans="1:42">
-      <c r="A8" t="s">
+      <c r="A8" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B8">
@@ -2469,7 +2477,7 @@
       </c>
     </row>
     <row r="10" spans="1:42">
-      <c r="A10" t="s">
+      <c r="A10" s="8" t="s">
         <v>75</v>
       </c>
       <c r="B10">
@@ -2594,7 +2602,7 @@
       </c>
     </row>
     <row r="11" spans="1:42">
-      <c r="A11" t="s">
+      <c r="A11" s="8" t="s">
         <v>78</v>
       </c>
       <c r="B11">
@@ -3094,7 +3102,7 @@
       </c>
     </row>
     <row r="15" spans="1:42">
-      <c r="A15" t="s">
+      <c r="A15" s="8" t="s">
         <v>90</v>
       </c>
       <c r="B15">
@@ -3219,7 +3227,7 @@
       </c>
     </row>
     <row r="16" spans="1:42">
-      <c r="A16" t="s">
+      <c r="A16" s="8" t="s">
         <v>93</v>
       </c>
       <c r="B16">
@@ -3969,7 +3977,7 @@
       </c>
     </row>
     <row r="22" spans="1:42">
-      <c r="A22" t="s">
+      <c r="A22" s="8" t="s">
         <v>105</v>
       </c>
       <c r="B22">
@@ -4094,7 +4102,7 @@
       </c>
     </row>
     <row r="23" spans="1:42">
-      <c r="A23" t="s">
+      <c r="A23" s="8" t="s">
         <v>106</v>
       </c>
       <c r="B23">
@@ -5225,7 +5233,7 @@
       </c>
     </row>
     <row r="32" spans="1:42">
-      <c r="A32" t="s">
+      <c r="A32" s="8" t="s">
         <v>128</v>
       </c>
       <c r="B32">
@@ -5350,7 +5358,7 @@
       </c>
     </row>
     <row r="33" spans="1:42">
-      <c r="A33" t="s">
+      <c r="A33" s="8" t="s">
         <v>130</v>
       </c>
       <c r="B33">
@@ -5850,7 +5858,7 @@
       </c>
     </row>
     <row r="37" spans="1:42">
-      <c r="A37" t="s">
+      <c r="A37" s="8" t="s">
         <v>143</v>
       </c>
       <c r="B37">
@@ -6100,7 +6108,7 @@
       </c>
     </row>
     <row r="39" spans="1:42">
-      <c r="A39" t="s">
+      <c r="A39" s="8" t="s">
         <v>148</v>
       </c>
       <c r="B39">
@@ -6350,7 +6358,7 @@
       </c>
     </row>
     <row r="41" spans="1:42">
-      <c r="A41" t="s">
+      <c r="A41" s="8" t="s">
         <v>153</v>
       </c>
       <c r="B41">
@@ -6469,7 +6477,7 @@
       </c>
     </row>
     <row r="42" spans="1:42">
-      <c r="A42" s="3" t="s">
+      <c r="A42" s="9" t="s">
         <v>155</v>
       </c>
       <c r="B42">
@@ -6844,7 +6852,7 @@
       </c>
     </row>
     <row r="45" spans="1:42">
-      <c r="A45" t="s">
+      <c r="A45" s="8" t="s">
         <v>164</v>
       </c>
       <c r="B45">
@@ -6969,7 +6977,7 @@
       </c>
     </row>
     <row r="46" spans="1:42">
-      <c r="A46" t="s">
+      <c r="A46" s="8" t="s">
         <v>165</v>
       </c>
       <c r="B46">
@@ -7344,7 +7352,7 @@
       </c>
     </row>
     <row r="49" spans="1:42">
-      <c r="A49" t="s">
+      <c r="A49" s="8" t="s">
         <v>168</v>
       </c>
       <c r="B49">
